--- a/artfynd/A 53571-2024 artfynd.xlsx
+++ b/artfynd/A 53571-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>81770047</v>
       </c>
       <c r="B2" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613292.1251332769</v>
+        <v>613292</v>
       </c>
       <c r="R2" t="n">
-        <v>6737142.003960337</v>
+        <v>6737142</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +769,313 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>109443738</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stävlet, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>613117</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6737052</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>81770092</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104803</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220461</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsbräsma</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cardamine flexuosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>With.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gävle-Kringlan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>613283</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6736826</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Barbara Kühn, Kajsa Mattsson, Anna Broberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>81769831</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gävle-Kringlan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>613165</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6737089</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Barbara Kühn, Kajsa Mattsson, Anna Broberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53571-2024 artfynd.xlsx
+++ b/artfynd/A 53571-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81770047</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109443738</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81770092</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81769831</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>